--- a/buildplan_generator/output/25-094 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-094 GENERATED BUILD PLAN.xlsx
@@ -74,12 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -88,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-109, 24-028, 24-032, 24-030, 24-029</t>
+          <t>23-060, 25-096, 25-097, 25-113, 25-109</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>1.5</v>
+      <c r="F9" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>1.0-9.2</t>
+          <t>ratio=0.75 (0.50-0.88)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,17 +757,17 @@
       <c r="E10" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>2</v>
+      <c r="F10" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=0.62 (0.50-0.86)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -813,8 +811,8 @@
       <c r="E12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>5</v>
+      <c r="F12" s="9" t="n">
+        <v>4.4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -823,7 +821,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>3.5-7.0</t>
+          <t>ratio=0.88 (0.75-1.00)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -850,8 +848,8 @@
       <c r="E13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>2.5</v>
+      <c r="F13" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -860,7 +858,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>0.8-7.5</t>
+          <t>ratio=1.00 (0.38-1.00)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -905,16 +903,16 @@
         <v>3</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-46.5</t>
+          <t>ratio=0.30 (0.30-1.10)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -958,7 +956,7 @@
       <c r="E17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -968,7 +966,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1012,8 +1010,8 @@
       <c r="E19" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>2</v>
+      <c r="F19" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1022,7 +1020,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2.0-7.0</t>
+          <t>ratio=1.00 (0.50-1.25)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1049,17 +1047,17 @@
       <c r="E20" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="9" t="n">
-        <v>3</v>
+      <c r="F20" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-49.5</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1084,17 +1082,15 @@
         </is>
       </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1138,8 +1134,8 @@
       <c r="E23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>2.5</v>
+      <c r="F23" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1148,7 +1144,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-12.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1175,8 +1171,8 @@
       <c r="E24" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F24" s="10" t="n">
-        <v>3</v>
+      <c r="F24" s="9" t="n">
+        <v>3.4</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1185,7 +1181,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>2.5-3.0</t>
+          <t>ratio=0.57 (0.36-1.00)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1213,16 +1209,16 @@
         <v>6</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1250,16 +1246,16 @@
         <v>12</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>1.5-2.0</t>
+          <t>ratio=0.79 (n=1)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1287,16 +1283,16 @@
         <v>1</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1340,8 +1336,8 @@
       <c r="E29" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="9" t="n">
-        <v>1.5</v>
+      <c r="F29" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1350,7 +1346,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-25.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1375,17 +1371,15 @@
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
-      <c r="F30" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1429,8 +1423,8 @@
       <c r="E32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>0.5</v>
+      <c r="F32" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1439,7 +1433,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=3.50 (1.00-3.50)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1466,8 +1460,8 @@
       <c r="E33" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>7.2</v>
+      <c r="F33" s="9" t="n">
+        <v>10.8</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1476,7 +1470,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>6.0-7.5</t>
+          <t>ratio=2.15 (0.88-2.40)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1504,12 +1498,12 @@
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1536,8 +1530,8 @@
       <c r="E35" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>3</v>
+      <c r="F35" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1546,7 +1540,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=0.80 (0.71-0.80)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1574,12 +1568,12 @@
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1624,16 +1618,16 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-24.0</t>
+          <t>ratio=5.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1661,12 +1655,12 @@
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1694,16 +1688,16 @@
         <v>1</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-25.0</t>
+          <t>ratio=3.00 (2.00-3.00)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1717,7 +1711,7 @@
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>59</v>
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>
@@ -1785,7 +1779,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-109, 24-028, 24-032, 24-030, 24-029</t>
+          <t>23-060, 25-096, 25-097, 25-113, 25-109</t>
         </is>
       </c>
     </row>
@@ -2731,35 +2725,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-109</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-028</t>
+          <t>25-096</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-032</t>
+          <t>25-097</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-030</t>
+          <t>25-113</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-029</t>
+          <t>25-109</t>
         </is>
       </c>
     </row>
@@ -2814,23 +2808,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2848,19 +2838,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>24-028, 24-029, 24-030, 24-032, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2874,7 +2860,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2883,12 +2869,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0-9.2</t>
+          <t>ratio=0.75 (0.50-0.88)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-109, 25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -2904,21 +2890,21 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=0.62 (0.50-0.86)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-109</t>
+          <t>25-109, 25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2920,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2943,12 +2929,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.5-7.0</t>
+          <t>ratio=0.88 (0.75-1.00)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-113, 25-109, 25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2950,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2973,12 +2959,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.8-7.5</t>
+          <t>ratio=1.00 (0.38-1.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-109, 25-097, 25-096</t>
         </is>
       </c>
     </row>
@@ -2994,21 +2980,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>global:1.0-46.5</t>
+          <t>ratio=0.30 (0.30-1.10)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3019,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24-032, 24-030, 24-029, 24-028</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3040,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3063,12 +3049,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.0-7.0</t>
+          <t>ratio=1.00 (0.50-1.25)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -3084,21 +3070,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>global:0.5-49.5</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
@@ -3114,23 +3100,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3144,7 +3126,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,12 +3135,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>global:0.5-12.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3156,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,12 +3165,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.5-3.0</t>
+          <t>ratio=0.57 (0.36-1.00)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -3204,21 +3186,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
@@ -3234,21 +3216,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5-2.0</t>
+          <t>ratio=0.79 (n=1)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
@@ -3264,21 +3246,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-097, 25-096</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3276,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3303,12 +3285,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>global:0.5-25.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3324,23 +3306,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3354,7 +3332,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3363,12 +3341,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=3.50 (1.00-3.50)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3362,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.2</v>
+        <v>10.8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3393,12 +3371,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6.0-7.5</t>
+          <t>ratio=2.15 (0.88-2.40)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -3418,19 +3396,15 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>24-028, 24-029, 24-030, 24-032, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3444,7 +3418,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3453,12 +3427,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=0.80 (0.71-0.80)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-109, 24-032, 24-030, 24-029, 24-028</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -3478,19 +3452,15 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>24-028, 24-029, 24-030, 24-032, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3504,21 +3474,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>global:1.0-24.0</t>
+          <t>ratio=5.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>
@@ -3538,19 +3508,15 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>24-028, 24-029, 24-030, 24-032, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3564,21 +3530,21 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>global:1.0-25.0</t>
+          <t>ratio=3.00 (2.00-3.00)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-097, 25-096, 23-060</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-094 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-094 GENERATED BUILD PLAN.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-060, 25-096, 25-097, 25-113, 25-109</t>
+          <t>25-096, 25-097, 23-060, 25-109, 23-035</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-0.88)</t>
+          <t>ratio=0.75 (0.40-0.88)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.50-0.86)</t>
+          <t>ratio=0.75 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-1.00)</t>
+          <t>ratio=0.88 (0.75-1.38)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -903,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.30 (0.30-1.10)</t>
+          <t>ratio=0.65 (0.30-1.10)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -1011,7 +1011,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.25)</t>
+          <t>ratio=1.12 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1172,7 +1172,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.57 (0.36-1.00)</t>
+          <t>ratio=0.69 (0.36-1.00)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1209,7 +1209,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>ratio=1.12 (n=2)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1246,7 +1246,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.79 (n=1)</t>
+          <t>ratio=0.73 (n=2)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1424,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.50 (1.00-3.50)</t>
+          <t>ratio=2.75 (1.00-3.50)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1461,7 +1461,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.15 (0.88-2.40)</t>
+          <t>ratio=1.51 (0.71-2.40)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1531,7 +1531,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.71-0.80)</t>
+          <t>ratio=0.76 (0.25-0.80)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1618,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=5.00 (2.00-5.00)</t>
+          <t>ratio=3.50 (1.50-5.00)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>82.5</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-060, 25-096, 25-097, 25-113, 25-109</t>
+          <t>25-096, 25-097, 23-060, 25-109, 23-035</t>
         </is>
       </c>
     </row>
@@ -2725,35 +2725,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>25-096</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-096</t>
+          <t>25-097</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-097</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-113</t>
+          <t>25-109</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-109</t>
+          <t>23-035</t>
         </is>
       </c>
     </row>
@@ -2869,12 +2869,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-0.88)</t>
+          <t>ratio=0.75 (0.40-0.88)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 23-060</t>
+          <t>25-109, 25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.50-0.86)</t>
+          <t>ratio=0.75 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 23-060</t>
+          <t>25-109, 25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -2929,12 +2929,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-1.00)</t>
+          <t>ratio=0.88 (0.75-1.38)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-113, 25-109, 25-097, 25-096, 23-060</t>
+          <t>25-109, 25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=0.30 (0.30-1.10)</t>
+          <t>ratio=0.65 (0.30-1.10)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.25)</t>
+          <t>ratio=1.12 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,12 +3165,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=0.57 (0.36-1.00)</t>
+          <t>ratio=0.69 (0.36-1.00)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>ratio=1.12 (n=2)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=0.79 (n=1)</t>
+          <t>ratio=0.73 (n=2)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=3.50 (1.00-3.50)</t>
+          <t>ratio=2.75 (1.00-3.50)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=2.15 (0.88-2.40)</t>
+          <t>ratio=1.51 (0.71-2.40)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.71-0.80)</t>
+          <t>ratio=0.76 (0.25-0.80)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=5.00 (2.00-5.00)</t>
+          <t>ratio=3.50 (1.50-5.00)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060</t>
+          <t>25-097, 25-096, 23-060, 23-035</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-094 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-094 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +76,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-096, 25-097, 23-060, 25-109, 23-035</t>
+          <t>23-060, 25-111, 25-113, 25-110, 25-096</t>
         </is>
       </c>
     </row>
@@ -638,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.40-0.88)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +751,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.50)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -812,7 +805,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -821,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-1.38)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -849,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -858,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.38-1.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -903,7 +896,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -912,7 +905,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.65 (0.30-1.10)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -956,17 +949,17 @@
       <c r="E17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1011,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>5.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1020,7 +1013,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.50-1.50)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1047,17 +1040,17 @@
       <c r="E20" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>6</v>
+      <c r="F20" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1085,12 +1078,12 @@
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1134,17 +1127,17 @@
       <c r="E23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>1</v>
+      <c r="F23" s="9" t="n">
+        <v>0.6</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1172,7 +1165,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1181,7 +1174,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.69 (0.36-1.00)</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1208,17 +1201,17 @@
       <c r="E25" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>6.8</v>
+      <c r="F25" s="9" t="n">
+        <v>2.8</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (n=2)</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1245,17 +1238,17 @@
       <c r="E26" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>8.800000000000001</v>
+      <c r="F26" s="9" t="n">
+        <v>5.5</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.73 (n=2)</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1282,17 +1275,17 @@
       <c r="E27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>1</v>
+      <c r="F27" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1336,17 +1329,17 @@
       <c r="E29" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="11" t="n">
-        <v>1</v>
+      <c r="F29" s="9" t="n">
+        <v>0.6</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1374,12 +1367,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1424,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1433,7 +1426,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.75 (1.00-3.50)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1461,7 +1454,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1470,7 +1463,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.51 (0.71-2.40)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1498,12 +1491,12 @@
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1531,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3.8</v>
+        <v>11.9</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1540,7 +1533,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.76 (0.25-0.80)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1568,12 +1561,12 @@
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1618,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1627,7 +1620,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.50 (1.50-5.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1655,12 +1648,12 @@
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1688,7 +1681,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1697,7 +1690,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-3.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1711,7 +1704,7 @@
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>77.90000000000001</v>
+        <v>71.2</v>
       </c>
     </row>
   </sheetData>
@@ -1779,7 +1772,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-096, 25-097, 23-060, 25-109, 23-035</t>
+          <t>23-060, 25-111, 25-113, 25-110, 25-096</t>
         </is>
       </c>
     </row>
@@ -2725,35 +2718,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-096</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-097</t>
+          <t>25-111</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>25-113</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-109</t>
+          <t>25-110</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-035</t>
+          <t>25-096</t>
         </is>
       </c>
     </row>
@@ -2812,15 +2805,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2838,15 +2835,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2860,7 +2861,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2869,12 +2870,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.40-0.88)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 23-060, 23-035</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2891,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2899,12 +2900,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.50)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 23-060, 23-035</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2921,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2929,12 +2930,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-1.38)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 23-060, 23-035</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2951,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2959,12 +2960,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.38-1.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2981,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2989,12 +2990,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=0.65 (0.30-1.10)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -3014,17 +3015,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3041,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3049,12 +3050,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.50-1.50)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3070,21 +3071,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23-060, 23-035</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3104,15 +3105,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3126,21 +3131,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3161,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,12 +3170,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=0.69 (0.36-1.00)</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3186,21 +3191,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.12 (n=2)</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23-060, 23-035</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3216,21 +3221,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=0.73 (n=2)</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>23-060, 23-035</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3246,21 +3251,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-097, 25-096</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3276,21 +3281,21 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3310,15 +3315,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3332,7 +3341,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3341,12 +3350,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=2.75 (1.00-3.50)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3371,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3371,12 +3380,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.51 (0.71-2.40)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -3396,15 +3405,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3418,7 +3431,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.8</v>
+        <v>11.9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3427,12 +3440,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.76 (0.25-0.80)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -3452,15 +3465,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3474,7 +3491,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3483,12 +3500,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=3.50 (1.50-5.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -3508,15 +3525,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3530,7 +3551,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3539,12 +3560,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-3.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 23-060, 23-035</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-094 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-094 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -805,7 +805,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -896,7 +896,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -1041,7 +1041,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1165,7 +1165,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1202,7 +1202,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1239,7 +1239,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1330,7 +1330,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1417,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1454,7 +1454,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1524,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>71.2</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:16h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
